--- a/vocafile/Hackers_Voca_Day4_with_Synonyms.xlsx
+++ b/vocafile/Hackers_Voca_Day4_with_Synonyms.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이태범\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92CB9B1D-B5C7-4F1F-A6D4-B65AA737FB7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A434F57-0FC4-499F-A15C-8BD11B27D5F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,9 +49,6 @@
     <t>adv.</t>
   </si>
   <si>
-    <t>1. easily, effortlessly; quickly</t>
-  </si>
-  <si>
     <t>reliable, trustworthy</t>
   </si>
   <si>
@@ -91,9 +88,6 @@
     <t>famous, celebrated, prominent, eminent</t>
   </si>
   <si>
-    <t>2. difficult to handle</t>
-  </si>
-  <si>
     <t>prevent, hinder, avert</t>
   </si>
   <si>
@@ -103,9 +97,6 @@
     <t>enormous</t>
   </si>
   <si>
-    <t>1. promote, speak in favor of, argue in support of</t>
-  </si>
-  <si>
     <t>huge, very large, great, immense, vast, tremendous</t>
   </si>
   <si>
@@ -139,9 +130,6 @@
     <t>period, epoch, age</t>
   </si>
   <si>
-    <t>2. breach, discord</t>
-  </si>
-  <si>
     <t>adaptable, flexible</t>
   </si>
   <si>
@@ -166,9 +154,6 @@
     <t>convince, induce</t>
   </si>
   <si>
-    <t>1. extensive, mass</t>
-  </si>
-  <si>
     <t>readily</t>
   </si>
   <si>
@@ -355,15 +340,9 @@
     <t>융통성 있는, 다방면의</t>
   </si>
   <si>
-    <t>1. impressive</t>
-  </si>
-  <si>
     <t>의무를 지우다, 강요하다</t>
   </si>
   <si>
-    <t>2. completely</t>
-  </si>
-  <si>
     <t>flow, current</t>
   </si>
   <si>
@@ -484,12 +463,6 @@
     <t>subsequent, following, succeeding</t>
   </si>
   <si>
-    <t>1. burst, break apart, split, tear</t>
-  </si>
-  <si>
-    <t>2. willingly, without reluctance</t>
-  </si>
-  <si>
     <t>force, coerce, compel, constrain</t>
   </si>
   <si>
@@ -499,9 +472,6 @@
     <t>unaffordable, extreme, exorbitant</t>
   </si>
   <si>
-    <t>2. proponent, supporter, upholder</t>
-  </si>
-  <si>
     <t>dismiss, disperse, break up</t>
   </si>
   <si>
@@ -590,6 +560,46 @@
   </si>
   <si>
     <t>new, innovative, unusual</t>
+  </si>
+  <si>
+    <t>easily, effortlessly; quickly</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>willingly, without reluctance</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>promote, speak in favor of, argue in support of</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>proponent, supporter, upholder</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>impressive</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>difficult to handle</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>extensive, mass</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>completely</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>burst, break apart, split, tear</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>breach, discord</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -979,6 +989,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E63"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <cols>
+    <col min="4" max="4" width="46" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
@@ -1002,16 +1015,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1019,16 +1032,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1036,16 +1049,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>27</v>
+        <v>182</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1053,16 +1066,16 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1070,16 +1083,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1087,16 +1100,16 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1104,16 +1117,16 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>111</v>
+        <v>184</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1121,16 +1134,16 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>23</v>
+        <v>185</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1138,16 +1151,16 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1155,16 +1168,16 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1172,16 +1185,16 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1189,16 +1202,16 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1206,16 +1219,16 @@
         <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1223,16 +1236,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>158</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1240,16 +1253,16 @@
         <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1257,16 +1270,16 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1274,16 +1287,16 @@
         <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1291,16 +1304,16 @@
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1308,16 +1321,16 @@
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1325,16 +1338,16 @@
         <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1342,16 +1355,16 @@
         <v>18</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1359,16 +1372,16 @@
         <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1376,16 +1389,16 @@
         <v>20</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1393,16 +1406,16 @@
         <v>21</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1410,16 +1423,16 @@
         <v>22</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1427,16 +1440,16 @@
         <v>23</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1444,16 +1457,16 @@
         <v>24</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1461,16 +1474,16 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1478,16 +1491,16 @@
         <v>26</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>48</v>
+        <v>186</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1495,16 +1508,16 @@
         <v>26</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>113</v>
+        <v>187</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1512,16 +1525,16 @@
         <v>27</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1529,16 +1542,16 @@
         <v>28</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1546,16 +1559,16 @@
         <v>29</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1563,16 +1576,16 @@
         <v>30</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1580,16 +1593,16 @@
         <v>31</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1597,16 +1610,16 @@
         <v>32</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1614,16 +1627,16 @@
         <v>33</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1631,16 +1644,16 @@
         <v>34</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1648,16 +1661,16 @@
         <v>35</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>154</v>
+        <v>188</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1665,16 +1678,16 @@
         <v>35</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>39</v>
+        <v>189</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1682,16 +1695,16 @@
         <v>36</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D42" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1699,16 +1712,16 @@
         <v>37</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1716,16 +1729,16 @@
         <v>38</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1733,16 +1746,16 @@
         <v>39</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1750,16 +1763,16 @@
         <v>40</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1767,16 +1780,16 @@
         <v>41</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1784,16 +1797,16 @@
         <v>42</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1801,16 +1814,16 @@
         <v>43</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D49" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1818,16 +1831,16 @@
         <v>44</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -1835,16 +1848,16 @@
         <v>45</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -1852,16 +1865,16 @@
         <v>46</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -1869,16 +1882,16 @@
         <v>47</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1886,16 +1899,16 @@
         <v>48</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -1903,16 +1916,16 @@
         <v>49</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -1920,16 +1933,16 @@
         <v>50</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -1937,16 +1950,16 @@
         <v>51</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -1954,16 +1967,16 @@
         <v>52</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -1971,16 +1984,16 @@
         <v>53</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -1988,16 +2001,16 @@
         <v>54</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2005,16 +2018,16 @@
         <v>55</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2022,16 +2035,16 @@
         <v>56</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -2039,16 +2052,16 @@
         <v>57</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
